--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135843075</v>
+        <v>136868474</v>
       </c>
       <c r="B3" t="n">
-        <v>92023</v>
+        <v>79555</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3242</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitplätt</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaetodermella luna</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mustalompolo, T lm</t>
+          <t>Tallskogar längs med E10, V om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>751341</v>
+        <v>751187</v>
       </c>
       <c r="R3" t="n">
-        <v>7518398</v>
+        <v>7518486</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:13</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:13</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -883,69 +873,74 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Äldre, lövrik tallskog på blåbärsris</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Christina Boyd</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135843075</t>
+          <t>https://artportalen.se/Sighting/136868474</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135842136</v>
+        <v>135843075</v>
       </c>
       <c r="B4" t="n">
-        <v>99147</v>
+        <v>92023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>223049</v>
+        <v>3242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Vitplätt</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Chaetodermella luna</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell ex D.P.Rogers &amp; H.S.Jacks.) Rauschert</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bergsmannijoki, Bergsmannijoki, T lm</t>
+          <t>Mustalompolo, T lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>751233</v>
+        <v>751341</v>
       </c>
       <c r="R4" t="n">
-        <v>7518470</v>
+        <v>7518398</v>
       </c>
       <c r="S4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,65 +994,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Christina Boyd</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka</t>
+          <t>Christina Boyd, per-erik mukka, Anna Öhlund, Stefan Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135842136</t>
+          <t>https://artportalen.se/Sighting/135843075</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135842158</v>
+        <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>98392</v>
+        <v>92134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>223358</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bergsmannijoki, Bergsmannijoki, T lm</t>
+          <t>Tallskogar längs med E10, V om Svappavaara, T lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>751233</v>
+        <v>751169</v>
       </c>
       <c r="R5" t="n">
         <v>7518462</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1076,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>17:03</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1107,22 +1092,465 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Äldre, lövrik tallskog på blåbärsris</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/136868473</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136868472</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79476</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tallskogar längs med E10, V om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>751172</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7518470</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Äldre, lövrik tallskog på blåbärsris</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868472</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>135842136</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99147</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>223049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Ormbär</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Paris quadrifolia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bergsmannijoki, Bergsmannijoki, T lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>751233</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7518470</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135842136</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135842158</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98392</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bergsmannijoki, Bergsmannijoki, T lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>751233</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7518462</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Stefan Andersson, Anna Öhlund, Christina Boyd, per-erik mukka</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/135842158</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>136868468</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79499</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tallskogar längs med E10, V om Svappavaara, T lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>751622</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7518403</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kiruna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Torne lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Jukkasjärvi</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Luckig och gammal barrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rashid Kadhim</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136868468</t>
         </is>
       </c>
     </row>
@@ -1132,6 +1560,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136868474</v>
       </c>
       <c r="B3" t="n">
-        <v>79555</v>
+        <v>79559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868472</v>
       </c>
       <c r="B6" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136868468</v>
       </c>
       <c r="B9" t="n">
-        <v>79499</v>
+        <v>79503</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136868474</v>
       </c>
       <c r="B3" t="n">
-        <v>79559</v>
+        <v>79561</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>92136</v>
+        <v>92138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868472</v>
       </c>
       <c r="B6" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136868468</v>
       </c>
       <c r="B9" t="n">
-        <v>79503</v>
+        <v>79505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136868474</v>
       </c>
       <c r="B3" t="n">
-        <v>79561</v>
+        <v>79562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868472</v>
       </c>
       <c r="B6" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136868468</v>
       </c>
       <c r="B9" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136868474</v>
       </c>
       <c r="B3" t="n">
-        <v>79562</v>
+        <v>79564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868472</v>
       </c>
       <c r="B6" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136868468</v>
       </c>
       <c r="B9" t="n">
-        <v>79506</v>
+        <v>79508</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136868474</v>
       </c>
       <c r="B3" t="n">
-        <v>79564</v>
+        <v>79567</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868472</v>
       </c>
       <c r="B6" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136868468</v>
       </c>
       <c r="B9" t="n">
-        <v>79508</v>
+        <v>79511</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136868474</v>
       </c>
       <c r="B3" t="n">
-        <v>79567</v>
+        <v>79580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868472</v>
       </c>
       <c r="B6" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136868468</v>
       </c>
       <c r="B9" t="n">
-        <v>79511</v>
+        <v>79524</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136868474</v>
       </c>
       <c r="B3" t="n">
-        <v>79580</v>
+        <v>79582</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868472</v>
       </c>
       <c r="B6" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136868468</v>
       </c>
       <c r="B9" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136868474</v>
       </c>
       <c r="B3" t="n">
-        <v>79582</v>
+        <v>79592</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868472</v>
       </c>
       <c r="B6" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136868468</v>
       </c>
       <c r="B9" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136868474</v>
       </c>
       <c r="B3" t="n">
-        <v>79592</v>
+        <v>79595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868472</v>
       </c>
       <c r="B6" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136868468</v>
       </c>
       <c r="B9" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -1014,7 +1014,7 @@
         <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136868474</v>
       </c>
       <c r="B3" t="n">
-        <v>79595</v>
+        <v>79600</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868472</v>
       </c>
       <c r="B6" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136868468</v>
       </c>
       <c r="B9" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136868474</v>
       </c>
       <c r="B3" t="n">
-        <v>79600</v>
+        <v>79611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868472</v>
       </c>
       <c r="B6" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136868468</v>
       </c>
       <c r="B9" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 29171-2026 artfynd.xlsx
+++ b/artfynd/A 29171-2026 artfynd.xlsx
@@ -795,7 +795,7 @@
         <v>136868474</v>
       </c>
       <c r="B3" t="n">
-        <v>79611</v>
+        <v>79612</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>136868473</v>
       </c>
       <c r="B5" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>136868472</v>
       </c>
       <c r="B6" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1452,7 +1452,7 @@
         <v>136868468</v>
       </c>
       <c r="B9" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
